--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -896,37 +896,37 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-70</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>-87.5</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-52.941176470588</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.782608695652</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.307692307692</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.275862068965</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.725663716814</v>
+        <v>-87.301587301587</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="14">
+        <v>30</v>
+      </c>
+      <c r="G17" s="14">
         <v>29</v>
       </c>
-      <c r="G17" s="14">
-        <v>32</v>
-      </c>
       <c r="H17" s="15">
-        <v>-9.375</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I17" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J17" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.604651162790</v>
+        <v>-21.153846153846</v>
       </c>
       <c r="L17" s="15">
-        <v>-32.692307692307</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>6.060606060606</v>
+        <v>17.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-55.128205128205</v>
+        <v>-54.444444444444</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I18" s="14">
         <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>7.142857142857</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.042553191489</v>
+        <v>-86.842105263157</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.764705882352</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J19" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.510638297872</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="L19" s="15">
-        <v>53.571428571428</v>
+        <v>42.424242424242</v>
       </c>
       <c r="M19" s="15">
-        <v>43.333333333333</v>
+        <v>42.424242424242</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.867924528301</v>
+        <v>-16.071428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>100</v>
       </c>
       <c r="F20" s="14">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14">
         <v>3</v>
       </c>
-      <c r="G20" s="14">
-        <v>4</v>
-      </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
-        <v>20</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.352941176470</v>
+        <v>-80.952380952380</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.727272727272</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.607843137254</v>
+        <v>-25.252525252525</v>
       </c>
       <c r="I21" s="17">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J21" s="17">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.021276595744</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.970588235294</v>
+        <v>-17.197452229299</v>
       </c>
       <c r="M21" s="18">
-        <v>0.862068965517</v>
+        <v>0.775193798449</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.845360824742</v>
+        <v>-70.917225950783</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,10 +1189,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
         <v>0</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H23" s="15">
-        <v>-47.826086956521</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K23" s="15">
-        <v>-37.037037037037</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="L23" s="15">
-        <v>-37.037037037037</v>
+        <v>-40.625</v>
       </c>
       <c r="M23" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.666666666666</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G24" s="14">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.666666666666</v>
+        <v>6.779661016949</v>
       </c>
       <c r="I24" s="14">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J24" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.347826086956</v>
+        <v>-1.941747572815</v>
       </c>
       <c r="L24" s="15">
-        <v>2.325581395348</v>
+        <v>-3.809523809523</v>
       </c>
       <c r="M24" s="15">
-        <v>25.714285714285</v>
+        <v>23.170731707317</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
         <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.692307692307</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J25" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K25" s="15">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.047619047619</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>116.666666666667</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>23.809523809523</v>
+        <v>44.117647058823</v>
       </c>
       <c r="I26" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J26" s="14">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K26" s="15">
-        <v>39.215686274509</v>
+        <v>37.931034482758</v>
       </c>
       <c r="L26" s="15">
-        <v>16.393442622950</v>
+        <v>19.402985074626</v>
       </c>
       <c r="M26" s="15">
-        <v>-24.468085106383</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,28 +1388,28 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
@@ -1444,16 +1444,16 @@
         <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.333333333333</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.666666666666</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -878,8 +878,8 @@
       <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>-100</v>
       </c>
       <c r="M14" s="15">
         <v>-100</v>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -926,7 +926,7 @@
         <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-87.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
         <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-76.190476190476</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-48.387096774193</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.827586206896</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.301587301587</v>
+        <v>-86.956521739130</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-44.444444444444</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>3.448275862068</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I17" s="14">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="J17" s="14">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="K17" s="15">
-        <v>-21.153846153846</v>
+        <v>-17.1875</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.666666666666</v>
+        <v>-22.058823529411</v>
       </c>
       <c r="M17" s="15">
-        <v>17.142857142857</v>
+        <v>29.268292682926</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.444444444444</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-45.454545454545</v>
+        <v>-37.5</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.764705882352</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.764705882352</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.842105263157</v>
+        <v>-87.121212121212</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
         <v>4</v>
       </c>
-      <c r="D19" s="14">
-        <v>6</v>
-      </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.714285714285</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J19" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.320754716981</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L19" s="15">
-        <v>42.424242424242</v>
+        <v>50</v>
       </c>
       <c r="M19" s="15">
-        <v>42.424242424242</v>
+        <v>50</v>
       </c>
       <c r="N19" s="15">
-        <v>-16.071428571428</v>
+        <v>-5.263157894736</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>100</v>
-      </c>
-      <c r="F20" s="14">
-        <v>4</v>
-      </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
@@ -1125,13 +1125,13 @@
         <v>14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M20" s="15">
         <v>14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-80.952380952380</v>
+        <v>-85.185185185185</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-57.142857142857</v>
+        <v>5</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.252525252525</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="J21" s="17">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.076923076923</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.197452229299</v>
+        <v>-14.525139664804</v>
       </c>
       <c r="M21" s="18">
-        <v>0.775193798449</v>
+        <v>4.794520547945</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.917225950783</v>
+        <v>-69.881889763779</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1201,13 +1201,13 @@
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H23" s="15">
-        <v>-40</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J23" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K23" s="15">
-        <v>-42.424242424242</v>
+        <v>-37.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-40.625</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>13.636363636363</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>18.181818181818</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G24" s="14">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H24" s="15">
-        <v>6.779661016949</v>
+        <v>12.280701754386</v>
       </c>
       <c r="I24" s="14">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="J24" s="14">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.941747572815</v>
+        <v>3.389830508474</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.809523809523</v>
+        <v>3.389830508474</v>
       </c>
       <c r="M24" s="15">
-        <v>23.170731707317</v>
+        <v>31.182795698924</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>300</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
         <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.076923076923</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>42.857142857142</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>44.117647058823</v>
+        <v>18.421052631578</v>
       </c>
       <c r="I26" s="14">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J26" s="14">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="K26" s="15">
-        <v>37.931034482758</v>
+        <v>29.166666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>19.402985074626</v>
+        <v>19.230769230769</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.568627450980</v>
+        <v>-25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1412,7 +1412,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="L28" s="15">
-        <v>42.857142857142</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-75</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
         <v>-66.666666666666</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-78.571428571428</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>-76.190476190476</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>-47.058823529411</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-48.837209302325</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.631578947368</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.956521739130</v>
+        <v>-85.526315789473</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.882352941176</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I17" s="14">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.1875</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="L17" s="15">
-        <v>-22.058823529411</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="M17" s="15">
-        <v>29.268292682926</v>
+        <v>63.414634146341</v>
       </c>
       <c r="N17" s="15">
-        <v>-50</v>
+        <v>-45.528455284552</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-37.5</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>6.25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.526315789473</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.526315789473</v>
+        <v>-10</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.121212121212</v>
+        <v>-88.819875776397</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>75</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.166666666666</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I19" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.263157894736</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L19" s="15">
-        <v>50</v>
+        <v>31.818181818181</v>
       </c>
       <c r="M19" s="15">
-        <v>50</v>
+        <v>31.818181818181</v>
       </c>
       <c r="N19" s="15">
-        <v>-5.263157894736</v>
+        <v>-10.769230769230</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1119,19 +1119,19 @@
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-52.941176470588</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="M20" s="15">
         <v>14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.185185185185</v>
+        <v>-86.440677966101</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.166666666666</v>
+        <v>-22.680412371134</v>
       </c>
       <c r="I21" s="17">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="J21" s="17">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.047619047619</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.525139664804</v>
+        <v>-14.077669902912</v>
       </c>
       <c r="M21" s="18">
-        <v>4.794520547945</v>
+        <v>11.320754716981</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.881889763779</v>
+        <v>-69.535283993115</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
@@ -1207,7 +1207,7 @@
         <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-14.285714285714</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
         <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H23" s="15">
-        <v>-43.478260869565</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I23" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J23" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K23" s="15">
-        <v>-37.5</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="L23" s="15">
-        <v>-24.242424242424</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="M23" s="15">
-        <v>13.636363636363</v>
+        <v>27.272727272727</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F24" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G24" s="14">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H24" s="15">
-        <v>12.280701754386</v>
+        <v>20</v>
       </c>
       <c r="I24" s="14">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="J24" s="14">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="K24" s="15">
-        <v>3.389830508474</v>
+        <v>6.060606060606</v>
       </c>
       <c r="L24" s="15">
-        <v>3.389830508474</v>
+        <v>3.703703703703</v>
       </c>
       <c r="M24" s="15">
-        <v>31.182795698924</v>
+        <v>41.414141414141</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>300</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I25" s="14">
+        <v>26</v>
+      </c>
+      <c r="J25" s="14">
         <v>24</v>
       </c>
-      <c r="J25" s="14">
-        <v>21</v>
-      </c>
       <c r="K25" s="15">
-        <v>14.285714285714</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.111111111111</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-7.142857142857</v>
+        <v>120</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>18.421052631578</v>
+        <v>46.875</v>
       </c>
       <c r="I26" s="14">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J26" s="14">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K26" s="15">
-        <v>29.166666666666</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L26" s="15">
-        <v>19.230769230769</v>
+        <v>22.093023255814</v>
       </c>
       <c r="M26" s="15">
-        <v>-25</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>62.5</v>
+        <v>77.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
         <v>-83.333333333333</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.444444444444</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1529,10 +1529,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>-66.666666666666</v>
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.333333333333</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-71.428571428571</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>-55.555555555555</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>-40.540540540540</v>
+        <v>-35</v>
       </c>
       <c r="L16" s="15">
-        <v>-48.837209302325</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.619047619047</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.526315789473</v>
+        <v>-84.883720930232</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>15.384615384615</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.523809523809</v>
+        <v>-2.5</v>
       </c>
       <c r="I17" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J17" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K17" s="15">
-        <v>-12.987012987013</v>
+        <v>-7.228915662650</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.987012987013</v>
+        <v>-11.494252873563</v>
       </c>
       <c r="M17" s="15">
-        <v>63.414634146341</v>
+        <v>48.076923076923</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.528455284552</v>
+        <v>-46.153846153846</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-70</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.285714285714</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L18" s="15">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-10</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.819875776397</v>
+        <v>-89.944134078212</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>70</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.761904761904</v>
+        <v>28</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="J19" s="14">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.451612903225</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>31.818181818181</v>
+        <v>50</v>
       </c>
       <c r="M19" s="15">
-        <v>31.818181818181</v>
+        <v>63.043478260869</v>
       </c>
       <c r="N19" s="15">
-        <v>-10.769230769230</v>
+        <v>1.351351351351</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
         <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-57.894736842105</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M20" s="15">
-        <v>14.285714285714</v>
+        <v>37.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.440677966101</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G21" s="17">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.680412371134</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="J21" s="17">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.055555555555</v>
+        <v>-10.548523206751</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.077669902912</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="M21" s="18">
-        <v>11.320754716981</v>
+        <v>17.777777777777</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.535283993115</v>
+        <v>-67.633587786259</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,7 +1207,7 @@
         <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-40</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>-40.909090909090</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I23" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>-37.777777777777</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L23" s="15">
-        <v>-24.324324324324</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M23" s="15">
-        <v>27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>35.714285714285</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F24" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H24" s="15">
-        <v>20</v>
+        <v>18.965517241379</v>
       </c>
       <c r="I24" s="14">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="J24" s="14">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="K24" s="15">
-        <v>6.060606060606</v>
+        <v>4.666666666666</v>
       </c>
       <c r="L24" s="15">
-        <v>3.703703703703</v>
+        <v>6.081081081081</v>
       </c>
       <c r="M24" s="15">
-        <v>41.414141414141</v>
+        <v>41.441441441441</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>20</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J25" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K25" s="15">
-        <v>8.333333333333</v>
+        <v>20</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.129032258064</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>120</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>46.875</v>
+        <v>12.820512820512</v>
       </c>
       <c r="I26" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J26" s="14">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K26" s="15">
-        <v>36.363636363636</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>22.093023255814</v>
+        <v>15.151515151515</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.052631578947</v>
+        <v>-22.972972972973</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-55.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>80</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>77.777777777777</v>
+        <v>70</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>-83.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.736842105263</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
+        <v>0</v>
+      </c>
+      <c r="L30" s="15">
         <v>-50</v>
       </c>
-      <c r="L30" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.75</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
@@ -899,34 +899,34 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-64.285714285714</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.294117647058</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>-35</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.478260869565</v>
+        <v>-43.137254901960</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.909090909090</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.883720930232</v>
+        <v>-84.065934065934</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>83.333333333333</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H17" s="15">
-        <v>-2.5</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="I17" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J17" s="14">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.228915662650</v>
+        <v>-13.684210526315</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.494252873563</v>
+        <v>-17.171717171717</v>
       </c>
       <c r="M17" s="15">
-        <v>48.076923076923</v>
+        <v>43.859649122807</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.153846153846</v>
+        <v>-47.096774193548</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,7 +1019,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
         <v>-100</v>
@@ -1028,28 +1028,28 @@
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-70</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.739130434782</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.181818181818</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.739130434782</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.944134078212</v>
+        <v>-90.816326530612</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>70</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>28</v>
+        <v>20.689655172413</v>
       </c>
       <c r="I19" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J19" s="14">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K19" s="15">
-        <v>4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>50</v>
+        <v>41.379310344827</v>
       </c>
       <c r="M19" s="15">
-        <v>63.043478260869</v>
+        <v>54.716981132075</v>
       </c>
       <c r="N19" s="15">
-        <v>1.351351351351</v>
+        <v>-1.204819277108</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
         <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.105263157894</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.333333333333</v>
+        <v>-82.089552238806</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>71.428571428571</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.166666666666</v>
+        <v>2.105263157894</v>
       </c>
       <c r="I21" s="17">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="J21" s="17">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.548523206751</v>
+        <v>-13.257575757575</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.017543859649</v>
+        <v>-12.260536398467</v>
       </c>
       <c r="M21" s="18">
-        <v>17.777777777777</v>
+        <v>16.243654822335</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.633587786259</v>
+        <v>-67.655367231638</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1210,10 +1210,10 @@
         <v>-50</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
         <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>-21.052631578947</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I23" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K23" s="15">
-        <v>-30.434782608695</v>
+        <v>-32</v>
       </c>
       <c r="L23" s="15">
-        <v>-30.434782608695</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>3.030303030303</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.555555555555</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H24" s="15">
-        <v>18.965517241379</v>
+        <v>11.475409836065</v>
       </c>
       <c r="I24" s="14">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J24" s="14">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="K24" s="15">
-        <v>4.666666666666</v>
+        <v>3.048780487804</v>
       </c>
       <c r="L24" s="15">
-        <v>6.081081081081</v>
+        <v>7.643312101910</v>
       </c>
       <c r="M24" s="15">
-        <v>41.441441441441</v>
+        <v>37.398373983739</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
         <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>44.444444444444</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J25" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K25" s="15">
-        <v>20</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>-38.461538461538</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>12.820512820512</v>
+        <v>2.040816326530</v>
       </c>
       <c r="I26" s="14">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J26" s="14">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="K26" s="15">
-        <v>26.666666666666</v>
+        <v>21.495327102803</v>
       </c>
       <c r="L26" s="15">
-        <v>15.151515151515</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.972972972973</v>
+        <v>-21.686746987951</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,72 +1426,72 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>70</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>88.888888888888</v>
+        <v>90</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-57.142857142857</v>
@@ -1500,39 +1500,39 @@
         <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-85</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
@@ -1541,7 +1541,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.235294117647</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="15">
         <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1635,13 +1635,13 @@
         <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>83</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,16 +890,16 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
@@ -908,7 +908,7 @@
         <v>20</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -923,10 +923,10 @@
         <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-64.705882352941</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>8.333333333333</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J16" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.558139534883</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.137254901960</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.297872340425</v>
+        <v>-32</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.065934065934</v>
+        <v>-83.084577114427</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-58.333333333333</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G17" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.302325581395</v>
+        <v>11.904761904761</v>
       </c>
       <c r="I17" s="14">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="J17" s="14">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.684210526315</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.171717171717</v>
+        <v>-8.256880733944</v>
       </c>
       <c r="M17" s="15">
-        <v>43.859649122807</v>
+        <v>69.491525423728</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.096774193548</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
+      <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
         <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.931034482758</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.816326530612</v>
+        <v>-91.162790697674</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>20.689655172413</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>-2.105263157894</v>
       </c>
       <c r="L19" s="15">
-        <v>41.379310344827</v>
+        <v>36.764705882352</v>
       </c>
       <c r="M19" s="15">
-        <v>54.716981132075</v>
+        <v>63.157894736842</v>
       </c>
       <c r="N19" s="15">
-        <v>-1.204819277108</v>
+        <v>3.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>5</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>22</v>
+      <c r="E20" s="15">
+        <v>400</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>88.888888888888</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M20" s="15">
-        <v>33.333333333333</v>
+        <v>88.888888888888</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.089552238806</v>
+        <v>-75.714285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-44.444444444444</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F21" s="17">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="G21" s="17">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H21" s="18">
-        <v>2.105263157894</v>
+        <v>12.871287128712</v>
       </c>
       <c r="I21" s="17">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="J21" s="17">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.257575757575</v>
+        <v>-7.241379310344</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.260536398467</v>
+        <v>-6.597222222222</v>
       </c>
       <c r="M21" s="18">
-        <v>16.243654822335</v>
+        <v>29.951690821256</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.655367231638</v>
+        <v>-65.424164524421</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="14">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-11.764705882352</v>
+        <v>31.25</v>
       </c>
       <c r="I23" s="14">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J23" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K23" s="15">
-        <v>-32</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-37.037037037037</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M23" s="15">
-        <v>3.030303030303</v>
+        <v>31.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.285714285714</v>
+        <v>17.647058823529</v>
       </c>
       <c r="F24" s="14">
         <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="15">
-        <v>11.475409836065</v>
+        <v>7.936507936507</v>
       </c>
       <c r="I24" s="14">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="J24" s="14">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K24" s="15">
-        <v>3.048780487804</v>
+        <v>4.419889502762</v>
       </c>
       <c r="L24" s="15">
-        <v>7.643312101910</v>
+        <v>9.883720930232</v>
       </c>
       <c r="M24" s="15">
-        <v>37.398373983739</v>
+        <v>37.956204379562</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>2</v>
-      </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>85.714285714285</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I25" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K25" s="15">
-        <v>22.222222222222</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-8.333333333333</v>
+        <v>2.702702702702</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,54 +1344,54 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.882352941176</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H26" s="15">
-        <v>2.040816326530</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="J26" s="14">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="K26" s="15">
-        <v>21.495327102803</v>
+        <v>20</v>
       </c>
       <c r="L26" s="15">
-        <v>11.111111111111</v>
+        <v>18.032786885245</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.686746987951</v>
+        <v>-22.994652406417</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
@@ -1400,7 +1400,7 @@
         <v>20</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1415,10 +1415,10 @@
         <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>9</v>
       </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
       <c r="H28" s="15">
-        <v>28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
+        <v>11.764705882352</v>
+      </c>
+      <c r="L28" s="15">
         <v>58.333333333333</v>
       </c>
-      <c r="L28" s="15">
-        <v>90</v>
-      </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1497,10 +1497,10 @@
         <v>-57.142857142857</v>
       </c>
       <c r="M29" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.956521739130</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1635,13 +1635,13 @@
         <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>83</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>400</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
         <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="15">
-        <v>-22.727272727272</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.615384615384</v>
+        <v>-34.545454545454</v>
       </c>
       <c r="M16" s="15">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.084577114427</v>
+        <v>-83.255813953488</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>11.904761904761</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J17" s="14">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.660377358490</v>
+        <v>-4.424778761061</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.256880733944</v>
+        <v>-10</v>
       </c>
       <c r="M17" s="15">
-        <v>69.491525423728</v>
+        <v>74.193548387096</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.897959183673</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-62.5</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.833333333333</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.424242424242</v>
+        <v>-43.243243243243</v>
       </c>
       <c r="M18" s="15">
-        <v>-20.833333333333</v>
+        <v>-16</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.162790697674</v>
+        <v>-91.176470588235</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-15.384615384615</v>
+        <v>120</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
         <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>15.789473684210</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J19" s="14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.105263157894</v>
+        <v>2</v>
       </c>
       <c r="L19" s="15">
-        <v>36.764705882352</v>
+        <v>39.726027397260</v>
       </c>
       <c r="M19" s="15">
-        <v>63.157894736842</v>
+        <v>52.238805970149</v>
       </c>
       <c r="N19" s="15">
-        <v>3.333333333333</v>
+        <v>9.677419354838</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>350</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>88.888888888888</v>
+        <v>72.727272727272</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.727272727272</v>
+        <v>-24</v>
       </c>
       <c r="M20" s="15">
-        <v>88.888888888888</v>
+        <v>111.111111111111</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.714285714285</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>38.461538461538</v>
+        <v>31.578947368421</v>
       </c>
       <c r="F21" s="17">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G21" s="17">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>12.871287128712</v>
+        <v>21.505376344086</v>
       </c>
       <c r="I21" s="17">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="J21" s="17">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.241379310344</v>
+        <v>-5.501618122977</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.597222222222</v>
+        <v>-7.301587301587</v>
       </c>
       <c r="M21" s="18">
-        <v>29.951690821256</v>
+        <v>26.406926406926</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.424164524421</v>
+        <v>-65.48463356974</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
         <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>31.25</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I23" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J23" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.857142857142</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="L23" s="15">
-        <v>-20.689655172413</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="15">
-        <v>31.428571428571</v>
+        <v>17.073170731707</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>17.647058823529</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="H24" s="15">
-        <v>7.936507936507</v>
+        <v>-1.265822784810</v>
       </c>
       <c r="I24" s="14">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="J24" s="14">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="K24" s="15">
-        <v>4.419889502762</v>
+        <v>3.317535545023</v>
       </c>
       <c r="L24" s="15">
-        <v>9.883720930232</v>
+        <v>9.547738693467</v>
       </c>
       <c r="M24" s="15">
-        <v>37.956204379562</v>
+        <v>43.421052631578</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>55.555555555555</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J25" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K25" s="15">
-        <v>26.666666666666</v>
+        <v>16.216216216216</v>
       </c>
       <c r="L25" s="15">
-        <v>2.702702702702</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>30.769230769230</v>
+        <v>250</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>8.333333333333</v>
+        <v>14.893617021276</v>
       </c>
       <c r="I26" s="14">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="J26" s="14">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>20</v>
+        <v>27.419354838709</v>
       </c>
       <c r="L26" s="15">
-        <v>18.032786885245</v>
+        <v>14.492753623188</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.994652406417</v>
+        <v>-18.134715025906</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>5</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-80</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
         <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>11.764705882352</v>
+        <v>29.411764705882</v>
       </c>
       <c r="L28" s="15">
-        <v>58.333333333333</v>
+        <v>69.230769230769</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L29" s="15">
         <v>-57.142857142857</v>
@@ -1500,7 +1500,7 @@
         <v>-40</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.956521739130</v>
+        <v>-89.655172413793</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1529,10 +1529,10 @@
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,17 +1625,17 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="L33" s="15">
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>-64.705882352941</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.404255319148</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.545454545454</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-40</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.255813953488</v>
+        <v>-82.532751091703</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
-        <v>11.111111111111</v>
+        <v>5.405405405405</v>
       </c>
       <c r="I17" s="14">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J17" s="14">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.424778761061</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-10</v>
+        <v>-7.8125</v>
       </c>
       <c r="M17" s="15">
-        <v>74.193548387096</v>
+        <v>76.119402985074</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.897959183673</v>
+        <v>-46.118721461187</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.230769230769</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.243243243243</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M18" s="15">
-        <v>-16</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.176470588235</v>
+        <v>-90.551181102362</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>120</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>15.789473684210</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="I19" s="14">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K19" s="15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>39.726027397260</v>
+        <v>37.179487179487</v>
       </c>
       <c r="M19" s="15">
-        <v>52.238805970149</v>
+        <v>48.611111111111</v>
       </c>
       <c r="N19" s="15">
-        <v>9.677419354838</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>266.666666666667</v>
+        <v>125</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>72.727272727272</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-24</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M20" s="15">
-        <v>111.111111111111</v>
+        <v>122.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-75</v>
+        <v>-75.903614457831</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>31.578947368421</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" s="18">
-        <v>21.505376344086</v>
+        <v>6.382978723404</v>
       </c>
       <c r="I21" s="17">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="J21" s="17">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.501618122977</v>
+        <v>-4.229607250755</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.301587301587</v>
+        <v>-5.934718100890</v>
       </c>
       <c r="M21" s="18">
-        <v>26.406926406926</v>
+        <v>26.294820717131</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.48463356974</v>
+        <v>-65.317286652078</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
         <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>17.647058823529</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I23" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J23" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K23" s="15">
-        <v>-22.580645161290</v>
+        <v>-17.1875</v>
       </c>
       <c r="L23" s="15">
-        <v>-25</v>
+        <v>-25.352112676056</v>
       </c>
       <c r="M23" s="15">
-        <v>17.073170731707</v>
+        <v>23.255813953488</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
         <v>78</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.265822784810</v>
+        <v>2.631578947368</v>
       </c>
       <c r="I24" s="14">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="J24" s="14">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="K24" s="15">
-        <v>3.317535545023</v>
+        <v>4.424778761061</v>
       </c>
       <c r="L24" s="15">
-        <v>9.547738693467</v>
+        <v>8.256880733944</v>
       </c>
       <c r="M24" s="15">
-        <v>43.421052631578</v>
+        <v>42.168674698795</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-28.571428571428</v>
+        <v>75</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>30.769230769230</v>
+        <v>25</v>
       </c>
       <c r="I25" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K25" s="15">
-        <v>16.216216216216</v>
+        <v>21.951219512195</v>
       </c>
       <c r="L25" s="15">
-        <v>-6.521739130434</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G26" s="14">
         <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>14.893617021276</v>
+        <v>23.404255319148</v>
       </c>
       <c r="I26" s="14">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K26" s="15">
-        <v>27.419354838709</v>
+        <v>24.087591240875</v>
       </c>
       <c r="L26" s="15">
-        <v>14.492753623188</v>
+        <v>6.918238993710</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.134715025906</v>
+        <v>-18.269230769230</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,13 +1403,13 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.111111111111</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
         <v>100</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,10 +1438,10 @@
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
         <v>22</v>
@@ -1466,55 +1466,55 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M29" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.655172413793</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1526,22 +1526,22 @@
         <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-92</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-55.555555555555</v>
+        <v>-65.217391304347</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
         <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.528301886792</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.158730158730</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.176470588235</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.532751091703</v>
+        <v>-82.186234817813</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>14.285714285714</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>5.405405405405</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="I17" s="14">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J17" s="14">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.666666666666</v>
+        <v>-6.766917293233</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.8125</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M17" s="15">
-        <v>76.119402985074</v>
+        <v>72.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.118721461187</v>
+        <v>-47.008547008547</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="E18" s="15">
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="14">
+        <v>6</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="15">
         <v>100</v>
       </c>
-      <c r="F18" s="14">
-        <v>5</v>
-      </c>
-      <c r="G18" s="14">
-        <v>4</v>
-      </c>
-      <c r="H18" s="15">
+      <c r="I18" s="14">
         <v>25</v>
-      </c>
-      <c r="I18" s="14">
-        <v>24</v>
       </c>
       <c r="J18" s="14">
         <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.111111111111</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.461538461538</v>
+        <v>-37.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.111111111111</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.551181102362</v>
+        <v>-90.706319702602</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
         <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.428571428571</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="14">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J19" s="14">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>2.631578947368</v>
       </c>
       <c r="L19" s="15">
-        <v>37.179487179487</v>
+        <v>34.482758620689</v>
       </c>
       <c r="M19" s="15">
-        <v>48.611111111111</v>
+        <v>51.948051948051</v>
       </c>
       <c r="N19" s="15">
-        <v>7</v>
+        <v>3.539823008849</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>9</v>
@@ -1116,22 +1116,22 @@
         <v>125</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="14">
         <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>66.666666666666</v>
+        <v>75</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.076923076923</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M20" s="15">
-        <v>122.222222222222</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.903614457831</v>
+        <v>-75.581395348837</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G21" s="17">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>6.382978723404</v>
+        <v>12.903225806451</v>
       </c>
       <c r="I21" s="17">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="J21" s="17">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.229607250755</v>
+        <v>-5.042016806722</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.934718100890</v>
+        <v>-7.880434782608</v>
       </c>
       <c r="M21" s="18">
-        <v>26.294820717131</v>
+        <v>25.555555555555</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.317286652078</v>
+        <v>-65.513733468972</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>-40</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>11.111111111111</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I23" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J23" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.1875</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L23" s="15">
-        <v>-25.352112676056</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M23" s="15">
-        <v>23.255813953488</v>
+        <v>17.391304347826</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>5.263157894736</v>
       </c>
       <c r="F24" s="14">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H24" s="15">
-        <v>2.631578947368</v>
+        <v>6.172839506172</v>
       </c>
       <c r="I24" s="14">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="J24" s="14">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="K24" s="15">
-        <v>4.424778761061</v>
+        <v>4.489795918367</v>
       </c>
       <c r="L24" s="15">
-        <v>8.256880733944</v>
+        <v>9.401709401709</v>
       </c>
       <c r="M24" s="15">
-        <v>42.168674698795</v>
+        <v>43.820224719101</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>75</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>25</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I25" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J25" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K25" s="15">
-        <v>21.951219512195</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.660377358490</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F26" s="14">
         <v>58</v>
       </c>
       <c r="G26" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>23.404255319148</v>
+        <v>18.367346938775</v>
       </c>
       <c r="I26" s="14">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J26" s="14">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="K26" s="15">
-        <v>24.087591240875</v>
+        <v>18.589743589743</v>
       </c>
       <c r="L26" s="15">
-        <v>6.918238993710</v>
+        <v>4.519774011299</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.269230769230</v>
+        <v>-17.410714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>50</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>6</v>
       </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>29.411764705882</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>69.230769230769</v>
+        <v>76.923076923076</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
@@ -1497,7 +1497,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="M29" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N29" s="15">
         <v>-86.666666666666</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,10 +1520,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1538,7 +1538,7 @@
         <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
         <v>-88.461538461538</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
+        <v>2</v>
+      </c>
+      <c r="J31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="K31" s="15">
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -199,13 +199,13 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -851,55 +851,55 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+        <v>21</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -920,13 +920,13 @@
         <v>-20</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N15" s="15">
-        <v>-65.217391304347</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J16" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.137931034482</v>
+        <v>-21.875</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.158730158730</v>
+        <v>-21.875</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.888888888888</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.186234817813</v>
+        <v>-80.988593155893</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-53.846153846153</v>
+        <v>250</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H17" s="15">
-        <v>-2.631578947368</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I17" s="14">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="J17" s="14">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.766917293233</v>
+        <v>0.729927007299</v>
       </c>
       <c r="L17" s="15">
-        <v>-13.888888888888</v>
+        <v>-12.658227848101</v>
       </c>
       <c r="M17" s="15">
-        <v>72.222222222222</v>
+        <v>79.220779220779</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.008547008547</v>
+        <v>-44.354838709677</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
         <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-7.407407407407</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.5</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="M18" s="15">
-        <v>-19.354838709677</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.706319702602</v>
+        <v>-90.209790209790</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,69 +1060,69 @@
         <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>57.142857142857</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>12.5</v>
+        <v>52</v>
       </c>
       <c r="I19" s="14">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K19" s="15">
-        <v>2.631578947368</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>34.482758620689</v>
+        <v>31.958762886597</v>
       </c>
       <c r="M19" s="15">
-        <v>51.948051948051</v>
+        <v>60</v>
       </c>
       <c r="N19" s="15">
-        <v>3.539823008849</v>
+        <v>9.401709401709</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
         <v>21</v>
       </c>
       <c r="J20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>75</v>
+        <v>61.538461538461</v>
       </c>
       <c r="L20" s="15">
         <v>-22.222222222222</v>
@@ -1131,7 +1131,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.581395348837</v>
+        <v>-76.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.538461538461</v>
+        <v>84.210526315789</v>
       </c>
       <c r="F21" s="17">
         <v>105</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>12.903225806451</v>
+        <v>22.093023255814</v>
       </c>
       <c r="I21" s="17">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="J21" s="17">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.042016806722</v>
+        <v>-0.531914893617</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.880434782608</v>
+        <v>-6.265664160401</v>
       </c>
       <c r="M21" s="18">
-        <v>25.555555555555</v>
+        <v>29.411764705882</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.513733468972</v>
+        <v>-64.141898370086</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-80</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>-5.263157894736</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I23" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J23" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K23" s="15">
-        <v>-21.739130434782</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="L23" s="15">
-        <v>-30.769230769230</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>17.391304347826</v>
+        <v>27.659574468085</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>5.263157894736</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F24" s="14">
+        <v>90</v>
+      </c>
+      <c r="G24" s="14">
         <v>86</v>
       </c>
-      <c r="G24" s="14">
-        <v>81</v>
-      </c>
       <c r="H24" s="15">
-        <v>6.172839506172</v>
+        <v>4.651162790697</v>
       </c>
       <c r="I24" s="14">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="J24" s="14">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="K24" s="15">
-        <v>4.489795918367</v>
+        <v>4.868913857677</v>
       </c>
       <c r="L24" s="15">
-        <v>9.401709401709</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M24" s="15">
-        <v>43.820224719101</v>
+        <v>48.936170212766</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J25" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K25" s="15">
-        <v>17.391304347826</v>
+        <v>14.545454545454</v>
       </c>
       <c r="L25" s="15">
-        <v>0</v>
+        <v>14.545454545454</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-21.052631578947</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
         <v>58</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>18.367346938775</v>
+        <v>31.818181818181</v>
       </c>
       <c r="I26" s="14">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="J26" s="14">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="K26" s="15">
-        <v>18.589743589743</v>
+        <v>22.560975609756</v>
       </c>
       <c r="L26" s="15">
-        <v>4.519774011299</v>
+        <v>6.914893617021</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.410714285714</v>
+        <v>-15.899581589958</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,10 +1385,10 @@
         <v>34</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
@@ -1397,28 +1397,28 @@
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,136 +1426,136 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>27.777777777777</v>
+        <v>31.578947368421</v>
       </c>
       <c r="L28" s="15">
-        <v>76.923076923076</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M29" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.666666666666</v>
+        <v>-83.870967741935</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.461538461538</v>
+        <v>-85.185185185185</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1576,13 +1576,13 @@
         <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,22 +1608,22 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>83</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -199,13 +199,13 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>0</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -885,48 +885,48 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M15" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-71.428571428571</v>
+        <v>-67.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.875</v>
+        <v>-23.611111111111</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.875</v>
+        <v>-23.611111111111</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.024390243902</v>
+        <v>-36.046511627907</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.988593155893</v>
+        <v>-80.286738351254</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>19</v>
+      </c>
+      <c r="D17" s="14">
         <v>14</v>
       </c>
-      <c r="D17" s="14">
-        <v>4</v>
-      </c>
       <c r="E17" s="15">
-        <v>250</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G17" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>16.129032258064</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I17" s="14">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="J17" s="14">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="K17" s="15">
-        <v>0.729927007299</v>
+        <v>3.311258278145</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.658227848101</v>
+        <v>-8.235294117647</v>
       </c>
       <c r="M17" s="15">
-        <v>79.220779220779</v>
+        <v>87.951807228915</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.354838709677</v>
+        <v>-43.682310469314</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I18" s="14">
         <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.777777777777</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="M18" s="15">
-        <v>-9.677419354838</v>
+        <v>-20</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.209790209790</v>
+        <v>-90.728476821192</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>83.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="14">
         <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>52</v>
+        <v>46.153846153846</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="J19" s="14">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="K19" s="15">
-        <v>6.666666666666</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L19" s="15">
-        <v>31.958762886597</v>
+        <v>30.188679245283</v>
       </c>
       <c r="M19" s="15">
-        <v>60</v>
+        <v>58.620689655172</v>
       </c>
       <c r="N19" s="15">
-        <v>9.401709401709</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>61.538461538461</v>
+        <v>53.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.222222222222</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>133.333333333333</v>
+        <v>64.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-76.666666666666</v>
+        <v>-75.268817204301</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>84.210526315789</v>
+        <v>12.121212121212</v>
       </c>
       <c r="F21" s="17">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G21" s="17">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>22.093023255814</v>
+        <v>17</v>
       </c>
       <c r="I21" s="17">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="J21" s="17">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.531914893617</v>
+        <v>0.244498777506</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.265664160401</v>
+        <v>-4.872389791183</v>
       </c>
       <c r="M21" s="18">
-        <v>29.411764705882</v>
+        <v>30.158730158730</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.141898370086</v>
+        <v>-63.096309630963</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1230,31 +1230,31 @@
         <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>-23.529411764705</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J23" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.808219178082</v>
+        <v>-15.584415584415</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.571428571428</v>
+        <v>-26.966292134831</v>
       </c>
       <c r="M23" s="15">
-        <v>27.659574468085</v>
+        <v>35.416666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>9.090909090909</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H24" s="15">
-        <v>4.651162790697</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="J24" s="14">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="K24" s="15">
-        <v>4.868913857677</v>
+        <v>2.473498233215</v>
       </c>
       <c r="L24" s="15">
-        <v>12.903225806451</v>
+        <v>8.208955223880</v>
       </c>
       <c r="M24" s="15">
-        <v>48.936170212766</v>
+        <v>40.776699029126</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
         <v>25</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I25" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J25" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K25" s="15">
-        <v>14.545454545454</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>14.545454545454</v>
+        <v>17.241379310344</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,54 +1344,54 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="14">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>31.818181818181</v>
+        <v>1.818181818181</v>
       </c>
       <c r="I26" s="14">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="J26" s="14">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="K26" s="15">
-        <v>22.560975609756</v>
+        <v>18.994413407821</v>
       </c>
       <c r="L26" s="15">
-        <v>6.914893617021</v>
+        <v>5.970149253731</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.899581589958</v>
+        <v>-16.141732283464</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1403,22 +1403,22 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-16.666666666666</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,38 +1428,38 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
         <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>31.578947368421</v>
+        <v>42.105263157894</v>
       </c>
       <c r="L28" s="15">
-        <v>66.666666666666</v>
+        <v>68.75</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>22</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="M29" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.870967741935</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,26 +1510,26 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>22</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.185185185185</v>
+        <v>-82.758620689655</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,40 +1549,40 @@
         <v>38</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L31" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,22 +1608,22 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>83</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L14" s="15">
         <v>-66.666666666666</v>
@@ -885,299 +885,299 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="14">
+        <v>21</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L15" s="15">
         <v>80</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N15" s="15">
-        <v>-67.857142857142</v>
+        <v>-68.965517241379</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.611111111111</v>
+        <v>-17.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.611111111111</v>
+        <v>-15.068493150684</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.046511627907</v>
+        <v>-31.111111111111</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.286738351254</v>
+        <v>-78.546712802768</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>35.714285714285</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>21.052631578947</v>
+        <v>20.512820512820</v>
       </c>
       <c r="I17" s="14">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="J17" s="14">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="K17" s="15">
-        <v>3.311258278145</v>
+        <v>3.773584905660</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.235294117647</v>
+        <v>-5.172413793103</v>
       </c>
       <c r="M17" s="15">
-        <v>87.951807228915</v>
+        <v>81.318681318681</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.682310469314</v>
+        <v>-43.103448275862</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-9.677419354838</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="L18" s="15">
-        <v>-40.425531914893</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="M18" s="15">
-        <v>-20</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.728476821192</v>
+        <v>-90.123456790123</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
+        <v>15</v>
+      </c>
+      <c r="D19" s="14">
         <v>10</v>
       </c>
-      <c r="D19" s="14">
-        <v>6</v>
-      </c>
       <c r="E19" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>46.153846153846</v>
+        <v>62.068965517241</v>
       </c>
       <c r="I19" s="14">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="J19" s="14">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K19" s="15">
-        <v>9.523809523809</v>
+        <v>12.5</v>
       </c>
       <c r="L19" s="15">
-        <v>30.188679245283</v>
+        <v>34.210526315789</v>
       </c>
       <c r="M19" s="15">
-        <v>58.620689655172</v>
+        <v>62.765957446808</v>
       </c>
       <c r="N19" s="15">
-        <v>15</v>
+        <v>21.428571428571</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>53.333333333333</v>
+        <v>68.75</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.857142857142</v>
+        <v>-10</v>
       </c>
       <c r="M20" s="15">
-        <v>64.285714285714</v>
+        <v>80</v>
       </c>
       <c r="N20" s="15">
-        <v>-75.268817204301</v>
+        <v>-72.448979591836</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>12.121212121212</v>
+        <v>50</v>
       </c>
       <c r="F21" s="17">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>17</v>
+        <v>28.846153846153</v>
       </c>
       <c r="I21" s="17">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="J21" s="17">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="K21" s="18">
-        <v>0.244498777506</v>
+        <v>3.218390804597</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.872389791183</v>
+        <v>-0.222222222222</v>
       </c>
       <c r="M21" s="18">
-        <v>30.158730158730</v>
+        <v>33.630952380952</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.096309630963</v>
+        <v>-61.591103507271</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1213,7 +1213,7 @@
         <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
         <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>6.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I23" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J23" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K23" s="15">
-        <v>-15.584415584415</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.966292134831</v>
+        <v>-26.881720430107</v>
       </c>
       <c r="M23" s="15">
-        <v>35.416666666666</v>
+        <v>28.301886792452</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="I24" s="14">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="J24" s="14">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="K24" s="15">
-        <v>2.473498233215</v>
+        <v>-0.649350649350</v>
       </c>
       <c r="L24" s="15">
-        <v>8.208955223880</v>
+        <v>6.993006993006</v>
       </c>
       <c r="M24" s="15">
-        <v>40.776699029126</v>
+        <v>43.661971830985</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14">
         <v>4</v>
       </c>
-      <c r="D25" s="14">
-        <v>5</v>
-      </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
         <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>8.695652173913</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I25" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J25" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K25" s="15">
-        <v>13.333333333333</v>
+        <v>10.9375</v>
       </c>
       <c r="L25" s="15">
-        <v>17.241379310344</v>
+        <v>14.516129032258</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H26" s="15">
-        <v>1.818181818181</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="I26" s="14">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="J26" s="14">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="K26" s="15">
-        <v>18.994413407821</v>
+        <v>11.557788944723</v>
       </c>
       <c r="L26" s="15">
-        <v>5.970149253731</v>
+        <v>5.714285714285</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.141732283464</v>
+        <v>-19.272727272727</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
         <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-8.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L27" s="15">
         <v>37.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,70 +1428,70 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>42.105263157894</v>
+        <v>31.818181818181</v>
       </c>
       <c r="L28" s="15">
-        <v>68.75</v>
+        <v>70.588235294117</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
         <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <v>3</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>200</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L29" s="15">
         <v>-25</v>
@@ -1500,39 +1500,39 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-81.818181818181</v>
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
+        <v>2</v>
+      </c>
+      <c r="H30" s="15">
         <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>200</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>-28.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-82.758620689655</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>83</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>1013</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1070</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1248</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>499</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>490</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>4469</v>

--- a/data/source/weekly/cs-en-us-032pct.xlsx
+++ b/data/source/weekly/cs-en-us-032pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -885,153 +885,153 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N15" s="15">
-        <v>-68.965517241379</v>
+        <v>-65.517241379310</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>133.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
         <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I16" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J16" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K16" s="15">
-        <v>-17.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.068493150684</v>
+        <v>-15.584415584415</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.111111111111</v>
+        <v>-30.851063829787</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.546712802768</v>
+        <v>-78.758169934640</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
-        <v>20.512820512820</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J17" s="14">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="K17" s="15">
-        <v>3.773584905660</v>
+        <v>1.807228915662</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.172413793103</v>
+        <v>-7.650273224043</v>
       </c>
       <c r="M17" s="15">
-        <v>81.318681318681</v>
+        <v>72.448979591836</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.103448275862</v>
+        <v>-46.006389776357</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="14">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
         <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="14">
         <v>32</v>
@@ -1043,177 +1043,177 @@
         <v>-3.030303030303</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.254901960784</v>
+        <v>-39.622641509434</v>
       </c>
       <c r="M18" s="15">
-        <v>-8.571428571428</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.123456790123</v>
+        <v>-90.670553935860</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>62.068965517241</v>
+        <v>45.161290322580</v>
       </c>
       <c r="I19" s="14">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J19" s="14">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K19" s="15">
-        <v>12.5</v>
+        <v>11.724137931034</v>
       </c>
       <c r="L19" s="15">
-        <v>34.210526315789</v>
+        <v>37.288135593220</v>
       </c>
       <c r="M19" s="15">
-        <v>62.765957446808</v>
+        <v>52.830188679245</v>
       </c>
       <c r="N19" s="15">
-        <v>21.428571428571</v>
+        <v>20.895522388059</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="14">
-        <v>5</v>
+        <v>27</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>75</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>68.75</v>
+        <v>47.058823529411</v>
       </c>
       <c r="L20" s="15">
-        <v>-10</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>80</v>
+        <v>56.25</v>
       </c>
       <c r="N20" s="15">
-        <v>-72.448979591836</v>
+        <v>-75.247524752475</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>28.846153846153</v>
+        <v>25</v>
       </c>
       <c r="I21" s="17">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="J21" s="17">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="K21" s="18">
-        <v>3.218390804597</v>
+        <v>1.531728665207</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.222222222222</v>
+        <v>-2.315789473684</v>
       </c>
       <c r="M21" s="18">
-        <v>33.630952380952</v>
+        <v>28.176795580110</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.591103507271</v>
+        <v>-62.610797743755</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
         <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>-11.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>68</v>
       </c>
       <c r="J23" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.073170731707</v>
+        <v>-21.839080459770</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.881720430107</v>
+        <v>-31.313131313131</v>
       </c>
       <c r="M23" s="15">
-        <v>28.301886792452</v>
+        <v>21.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
         <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-40</v>
+        <v>-8</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.634146341463</v>
+        <v>-17.045454545454</v>
       </c>
       <c r="I24" s="14">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="J24" s="14">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.649350649350</v>
+        <v>-1.201201201201</v>
       </c>
       <c r="L24" s="15">
-        <v>6.993006993006</v>
+        <v>9.666666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>43.661971830985</v>
+        <v>43.043478260869</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1312,31 +1312,31 @@
         <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.695652173913</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I25" s="14">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J25" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K25" s="15">
-        <v>10.9375</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L25" s="15">
-        <v>14.516129032258</v>
+        <v>15.625</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="F26" s="14">
         <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.129032258064</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="I26" s="14">
+        <v>236</v>
+      </c>
+      <c r="J26" s="14">
         <v>222</v>
       </c>
-      <c r="J26" s="14">
-        <v>199</v>
-      </c>
       <c r="K26" s="15">
-        <v>11.557788944723</v>
+        <v>6.306306306306</v>
       </c>
       <c r="L26" s="15">
-        <v>5.714285714285</v>
+        <v>4.424778761061</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.272727272727</v>
+        <v>-20.538720538720</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-15.384615384615</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L27" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K28" s="15">
-        <v>31.818181818181</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>70.588235294117</v>
+        <v>76.470588235294</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1494,13 +1494,13 @@
         <v>-14.285714285714</v>
       </c>
       <c r="L29" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-82.352941176470</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
@@ -1535,13 +1535,13 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M30" s="15">
         <v>-28.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.294117647058</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>100</v>
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>83</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>1013</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1070</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1248</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>499</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>490</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>4469</v>
